--- a/health_tracking_forms/034_meditation_habit_tracker--health_tracking_forms.xlsx
+++ b/health_tracking_forms/034_meditation_habit_tracker--health_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'focusing_on_breath'}</t>
+          <t>focusing_on_breath</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Focusing on breath'}</t>
+          <t>Focusing on breath</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'not_focusing_on_breath'}</t>
+          <t>not_focusing_on_breath</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Not focusing on breath'}</t>
+          <t>Not focusing on breath</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'mindful_movement'}</t>
+          <t>mindful_movement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Mindful movement'}</t>
+          <t>Mindful movement</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'mindfulness_meditation'}</t>
+          <t>mindfulness_meditation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Mindfulness meditation'}</t>
+          <t>Mindfulness meditation</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'loving-kindness_meditation'}</t>
+          <t>loving-kindness_meditation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Loving-Kindness meditation'}</t>
+          <t>Loving-Kindness meditation</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'movement_meditation'}</t>
+          <t>movement_meditation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Movement meditation'}</t>
+          <t>Movement meditation</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'guided_meditation'}</t>
+          <t>guided_meditation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Guided meditation'}</t>
+          <t>Guided meditation</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'reduce_stress'}</t>
+          <t>reduce_stress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Reduce stress'}</t>
+          <t>Reduce stress</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'increase_focus'}</t>
+          <t>increase_focus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Increase focus'}</t>
+          <t>Increase focus</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'improve_mood'}</t>
+          <t>improve_mood</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Improve mood'}</t>
+          <t>Improve mood</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'very_consistent'}</t>
+          <t>very_consistent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Very consistent'}</t>
+          <t>Very consistent</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'moderately_consistent'}</t>
+          <t>moderately_consistent</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Moderately consistent'}</t>
+          <t>Moderately consistent</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_inconsistent'}</t>
+          <t>somewhat_inconsistent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat inconsistent'}</t>
+          <t>Somewhat inconsistent</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_consistent'}</t>
+          <t>not_at_all_consistent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all consistent'}</t>
+          <t>Not at all consistent</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'made_progress'}</t>
+          <t>made_progress</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Made progress'}</t>
+          <t>Made progress</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_"didn't_make_progress"}</t>
+          <t>didn't_make_progress</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': "Didn't make progress"}</t>
+          <t>Didn't make progress</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_time'}</t>
+          <t>lack_of_time</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of time'}</t>
+          <t>Lack of time</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'distractions'}</t>
+          <t>distractions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Distractions'}</t>
+          <t>Distractions</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'reduced_stress'}</t>
+          <t>reduced_stress</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Reduced stress'}</t>
+          <t>Reduced stress</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'improved_focus'}</t>
+          <t>improved_focus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Improved focus'}</t>
+          <t>Improved focus</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'improved_mood'}</t>
+          <t>improved_mood</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Improved mood'}</t>
+          <t>Improved mood</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'improved_sleep'}</t>
+          <t>improved_sleep</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Improved sleep'}</t>
+          <t>Improved sleep</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'myself'}</t>
+          <t>myself</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Myself'}</t>
+          <t>Myself</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'a_coach_or_therapist'}</t>
+          <t>a_coach_or_therapist</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'A coach or therapist'}</t>
+          <t>A coach or therapist</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'someone_i_know'}</t>
+          <t>someone_i_know</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Someone I know'}</t>
+          <t>Someone I know</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'myself'}</t>
+          <t>myself</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Myself'}</t>
+          <t>Myself</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'a_coach_or_therapist'}</t>
+          <t>a_coach_or_therapist</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'A coach or therapist'}</t>
+          <t>A coach or therapist</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'someone_i_know'}</t>
+          <t>someone_i_know</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Someone I know'}</t>
+          <t>Someone I know</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
